--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_CAJA.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_CAJA.xlsx
@@ -3107,11 +3107,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="19813205"/>
-        <c:axId val="91492491"/>
+        <c:axId val="90119290"/>
+        <c:axId val="48359492"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="19813205"/>
+        <c:axId val="90119290"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -3145,7 +3145,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91492491"/>
+        <c:crossAx val="48359492"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -3157,7 +3157,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="91492491"/>
+        <c:axId val="48359492"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3200,7 +3200,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19813205"/>
+        <c:crossAx val="90119290"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5001,11 +5001,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="65796783"/>
-        <c:axId val="21277813"/>
+        <c:axId val="8832645"/>
+        <c:axId val="45496510"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="65796783"/>
+        <c:axId val="8832645"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5037,7 +5037,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21277813"/>
+        <c:crossAx val="45496510"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -5048,7 +5048,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="21277813"/>
+        <c:axId val="45496510"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -5133,7 +5133,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65796783"/>
+        <c:crossAx val="8832645"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8821,7 +8821,7 @@
       </c>
       <c r="AW20" s="32" t="n">
         <f aca="false">LOOKUP(AW19,$A$3:$A$2973,$B$3:$B$2973)</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="AX20" s="32" t="n">
         <f aca="false">LOOKUP(AX19,$A$3:$A$2973,$B$3:$B$2973)</f>
@@ -9079,7 +9079,7 @@
       </c>
       <c r="AH22" s="23" t="n">
         <f aca="false">+(S23/R23-1)</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AI22" s="10"/>
       <c r="AJ22" s="10"/>
@@ -9091,7 +9091,7 @@
       <c r="AP22" s="10"/>
       <c r="AQ22" s="24" t="n">
         <f aca="false">+(S23/P23-1)/COUNTA(AE22:AP22)*12</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="AV22" s="7" t="s">
         <v>26</v>
@@ -9145,7 +9145,7 @@
       </c>
       <c r="S23" s="4" t="n">
         <f aca="false">+B249</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="U23" s="20"/>
       <c r="Y23" s="20"/>
@@ -9648,23 +9648,23 @@
       </c>
       <c r="AX29" s="42" t="n">
         <f aca="false">($AW20/AX20-1)/(AW19-AX19)*30</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AY29" s="42" t="n">
         <f aca="false">$AW20/AY20-1</f>
-        <v>-0.248750231235289</v>
+        <v>-0.237979628862347</v>
       </c>
       <c r="AZ29" s="42" t="n">
         <f aca="false">$AW20/AZ20-1</f>
-        <v>-0.239809516977627</v>
+        <v>-0.228910732364632</v>
       </c>
       <c r="BA29" s="42" t="n">
         <f aca="false">$AW20/BA20-1</f>
-        <v>-0.220741912237796</v>
+        <v>-0.209569757039683</v>
       </c>
       <c r="BB29" s="42" t="n">
         <f aca="false">+AQ87</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="BC29" s="43"/>
       <c r="BD29" s="28"/>
@@ -14689,7 +14689,7 @@
       </c>
       <c r="AH87" s="54" t="n">
         <f aca="false">+AH22</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AI87" s="54"/>
       <c r="AJ87" s="54"/>
@@ -14701,7 +14701,7 @@
       <c r="AP87" s="54"/>
       <c r="AQ87" s="54" t="n">
         <f aca="false">+AQ22</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="88" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20786,15 +20786,15 @@
         <v>46142</v>
       </c>
       <c r="B249" s="4" t="n">
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="C249" s="26" t="n">
         <f aca="false">+(B249/B248-1)/(A249-A248)*30</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="D249" s="4" t="n">
         <f aca="false">B249/$B$3*100</f>
-        <v>179.266768079531</v>
+        <v>181.836900088812</v>
       </c>
       <c r="F249" s="18" t="n">
         <v>46142</v>
@@ -20928,23 +20928,23 @@
       </c>
       <c r="T2" s="80" t="n">
         <f aca="false">+'Datos ICP (2)'!AX29</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="U2" s="80" t="n">
         <f aca="false">+'Datos ICP (2)'!AY29</f>
-        <v>-0.248750231235289</v>
+        <v>-0.237979628862347</v>
       </c>
       <c r="V2" s="80" t="n">
         <f aca="false">+'Datos ICP (2)'!AZ29</f>
-        <v>-0.239809516977627</v>
+        <v>-0.228910732364632</v>
       </c>
       <c r="W2" s="80" t="n">
         <f aca="false">+'Datos ICP (2)'!BA29</f>
-        <v>-0.220741912237796</v>
+        <v>-0.209569757039683</v>
       </c>
       <c r="X2" s="80" t="n">
         <f aca="false">+'Datos ICP (2)'!BB29</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22896,7 +22896,7 @@
       </c>
       <c r="H38" s="91" t="n">
         <f aca="false">+'Datos ICP (2)'!AH87</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="I38" s="91"/>
       <c r="J38" s="91"/>
@@ -22908,7 +22908,7 @@
       <c r="P38" s="91"/>
       <c r="Q38" s="91" t="n">
         <f aca="false">+'Datos ICP (2)'!AQ87</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_CAJA.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_CAJA.xlsx
@@ -3107,11 +3107,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="90119290"/>
-        <c:axId val="48359492"/>
+        <c:axId val="74221451"/>
+        <c:axId val="34009004"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="90119290"/>
+        <c:axId val="74221451"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -3145,7 +3145,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48359492"/>
+        <c:crossAx val="34009004"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -3157,7 +3157,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="48359492"/>
+        <c:axId val="34009004"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3200,7 +3200,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90119290"/>
+        <c:crossAx val="74221451"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5001,11 +5001,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="8832645"/>
-        <c:axId val="45496510"/>
+        <c:axId val="54238570"/>
+        <c:axId val="53485324"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="8832645"/>
+        <c:axId val="54238570"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5037,7 +5037,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45496510"/>
+        <c:crossAx val="53485324"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -5048,7 +5048,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="45496510"/>
+        <c:axId val="53485324"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -5133,7 +5133,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8832645"/>
+        <c:crossAx val="54238570"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_CAJA.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_CAJA.xlsx
@@ -3107,11 +3107,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="74221451"/>
-        <c:axId val="34009004"/>
+        <c:axId val="67219234"/>
+        <c:axId val="33723100"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="74221451"/>
+        <c:axId val="67219234"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -3145,7 +3145,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34009004"/>
+        <c:crossAx val="33723100"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -3157,7 +3157,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="34009004"/>
+        <c:axId val="33723100"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3200,7 +3200,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74221451"/>
+        <c:crossAx val="67219234"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5001,11 +5001,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="54238570"/>
-        <c:axId val="53485324"/>
+        <c:axId val="98654901"/>
+        <c:axId val="37691718"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="54238570"/>
+        <c:axId val="98654901"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5037,7 +5037,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53485324"/>
+        <c:crossAx val="37691718"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -5048,7 +5048,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="53485324"/>
+        <c:axId val="37691718"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -5133,7 +5133,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54238570"/>
+        <c:crossAx val="98654901"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_CAJA.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_CAJA.xlsx
@@ -3107,11 +3107,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="67219234"/>
-        <c:axId val="33723100"/>
+        <c:axId val="18769630"/>
+        <c:axId val="47052308"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="67219234"/>
+        <c:axId val="18769630"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -3145,7 +3145,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33723100"/>
+        <c:crossAx val="47052308"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -3157,7 +3157,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="33723100"/>
+        <c:axId val="47052308"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3200,7 +3200,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67219234"/>
+        <c:crossAx val="18769630"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5001,11 +5001,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="98654901"/>
-        <c:axId val="37691718"/>
+        <c:axId val="62425195"/>
+        <c:axId val="93840303"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="98654901"/>
+        <c:axId val="62425195"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5037,7 +5037,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37691718"/>
+        <c:crossAx val="93840303"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -5048,7 +5048,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="37691718"/>
+        <c:axId val="93840303"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -5133,7 +5133,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="98654901"/>
+        <c:crossAx val="62425195"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
